--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_coquimbo.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:59</t>
+    <t xml:space="preserve">2026-09-24 00:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -567,10 +567,10 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>-0.03</v>
@@ -616,10 +616,10 @@
         <v>-0.08</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.67</v>
+        <v>-0.49</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>-0.02</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="6">
@@ -659,13 +659,13 @@
         <v>10</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>-0.02</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="7">
@@ -685,10 +685,10 @@
         <v>-0.14</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="8">
@@ -708,10 +708,10 @@
         <v>0.44</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="9">
@@ -731,10 +731,10 @@
         <v>0.47</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="10">
@@ -757,7 +757,7 @@
         <v>0.16</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="11">
@@ -774,7 +774,7 @@
         <v>16</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0.16</v>
@@ -797,13 +797,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="13">
@@ -823,10 +823,10 @@
         <v>-0.03</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="14">
@@ -843,13 +843,13 @@
         <v>16</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.51</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="15">
@@ -866,13 +866,13 @@
         <v>16</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="16">
@@ -892,10 +892,10 @@
         <v>-0.66</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="17">
@@ -912,13 +912,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>-0.32</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="18">
@@ -958,13 +958,13 @@
         <v>30</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.74</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="20">
@@ -984,10 +984,10 @@
         <v>0.77</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="21">
@@ -1010,7 +1010,7 @@
         <v>-0.04</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="22">
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>-0.36</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="23">
@@ -1050,13 +1050,13 @@
         <v>10</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.66</v>
+        <v>-0.64</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>-0.51</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="24">
@@ -1073,13 +1073,13 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.25</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>-0.26</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="25">
@@ -1096,13 +1096,13 @@
         <v>10</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0.29</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="26">
@@ -1119,13 +1119,13 @@
         <v>10</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0.42</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="27">
@@ -1145,10 +1145,10 @@
         <v>-0.38</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="28">
@@ -1168,10 +1168,10 @@
         <v>-0.48</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="29">
@@ -1191,10 +1191,10 @@
         <v>-0.46</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="30">
@@ -1211,13 +1211,13 @@
         <v>16</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="31">
@@ -1234,13 +1234,13 @@
         <v>16</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="32">
@@ -1257,13 +1257,13 @@
         <v>16</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="33">
@@ -1286,7 +1286,7 @@
         <v>0.25</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="34">
@@ -1303,13 +1303,13 @@
         <v>16</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="35">
@@ -1326,13 +1326,13 @@
         <v>16</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>-0.13</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1349,13 +1349,13 @@
         <v>16</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="37">
@@ -1372,13 +1372,13 @@
         <v>16</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>-0.18</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="38">
@@ -1418,13 +1418,13 @@
         <v>30</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.37</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="40">
@@ -1441,10 +1441,10 @@
         <v>30</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>0.21</v>
@@ -1884,7 +1884,7 @@
         <v>0.08</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="60">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_coquimbo.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:49</t>
+    <t xml:space="preserve">2026-10-01 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_coquimbo.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:11</t>
+    <t xml:space="preserve">2026-10-05 19:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
